--- a/MacroHack_data/ExtraData/IVBO_OKVED2_02-2026.xlsx
+++ b/MacroHack_data/ExtraData/IVBO_OKVED2_02-2026.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="77" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="48">
   <si>
     <t xml:space="preserve">Содержание:</t>
   </si>
@@ -343,38 +343,9 @@
     </r>
   </si>
   <si>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="12"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-        <charset val="204"/>
-      </rPr>
-      <t xml:space="preserve">Индекс выпуска товаров и услуг по базовым видам 
-экономической деятельности</t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <vertAlign val="superscript"/>
-        <sz val="12"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-        <charset val="204"/>
-      </rPr>
-      <t xml:space="preserve">1) 
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-        <charset val="204"/>
-      </rPr>
-      <t xml:space="preserve">(в постоянных ценах 2021 года, в % к предыдущему периоду)</t>
-    </r>
+    <t xml:space="preserve">Индекс выпуска товаров и услуг по базовым видам 
+экономической деятельности1) 
+(в постоянных ценах 2021 года, в % к предыдущему периоду)</t>
   </si>
   <si>
     <t xml:space="preserve">2013г.</t>
@@ -698,20 +669,24 @@
       <protection locked="true" hidden="false"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="43">
+  <cellXfs count="40">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -719,23 +694,23 @@
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="22" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="22" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="21" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="21" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -743,91 +718,83 @@
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="21" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="21" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="11" fillId="0" borderId="1" xfId="21" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="16" fillId="0" borderId="2" xfId="21" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="16" fillId="0" borderId="2" xfId="21" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="17" fillId="0" borderId="2" xfId="21" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="12" fillId="0" borderId="0" xfId="21" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="12" fillId="0" borderId="0" xfId="21" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="8" fillId="0" borderId="0" xfId="21" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="21" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="11" fillId="0" borderId="0" xfId="21" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="7" fillId="0" borderId="0" xfId="21" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="12" fillId="0" borderId="0" xfId="21" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="4" fillId="0" borderId="0" xfId="21" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="21" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="11" fillId="0" borderId="1" xfId="21" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="16" fillId="0" borderId="2" xfId="21" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="16" fillId="0" borderId="2" xfId="21" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="22" fillId="0" borderId="0" xfId="21" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="23" fillId="0" borderId="0" xfId="21" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="24" fillId="0" borderId="0" xfId="21" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="17" fillId="0" borderId="2" xfId="21" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="12" fillId="0" borderId="0" xfId="21" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="166" fontId="12" fillId="0" borderId="0" xfId="21" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="166" fontId="8" fillId="0" borderId="0" xfId="21" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="21" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="166" fontId="11" fillId="0" borderId="0" xfId="21" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="166" fontId="7" fillId="0" borderId="0" xfId="21" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="167" fontId="12" fillId="0" borderId="0" xfId="21" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="166" fontId="4" fillId="0" borderId="0" xfId="21" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="22" fillId="0" borderId="0" xfId="21" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="23" fillId="0" borderId="0" xfId="21" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="24" fillId="0" borderId="0" xfId="21" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="21" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="21" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="17" fillId="0" borderId="2" xfId="21" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="17" fillId="0" borderId="2" xfId="21" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -851,7 +818,7 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="false" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="26" fillId="0" borderId="0" xfId="21" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="26" fillId="0" borderId="0" xfId="21" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -859,15 +826,7 @@
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="false" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="21" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="27" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="27" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="27" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -898,9 +857,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
-      <xdr:colOff>681480</xdr:colOff>
+      <xdr:colOff>681120</xdr:colOff>
       <xdr:row>0</xdr:row>
-      <xdr:rowOff>416880</xdr:rowOff>
+      <xdr:rowOff>416520</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -916,7 +875,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="1428840" y="0"/>
-          <a:ext cx="390600" cy="416880"/>
+          <a:ext cx="390240" cy="416520"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -943,9 +902,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
-      <xdr:colOff>681480</xdr:colOff>
+      <xdr:colOff>681120</xdr:colOff>
       <xdr:row>0</xdr:row>
-      <xdr:rowOff>416880</xdr:rowOff>
+      <xdr:rowOff>416520</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -961,7 +920,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="1428840" y="0"/>
-          <a:ext cx="390600" cy="416880"/>
+          <a:ext cx="390240" cy="416520"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1160,222 +1119,222 @@
   <dimension ref="A1:M13"/>
   <sheetFormatPr defaultColWidth="8.54296875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="3.42"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="0" width="16.29"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="3.42"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="1" width="16.29"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2"/>
-      <c r="C1" s="2"/>
-      <c r="D1" s="2"/>
-      <c r="E1" s="2"/>
-      <c r="F1" s="2"/>
-      <c r="G1" s="2"/>
-      <c r="H1" s="2"/>
-      <c r="I1" s="2"/>
-      <c r="J1" s="2"/>
-      <c r="K1" s="2"/>
-      <c r="L1" s="2"/>
-      <c r="M1" s="2"/>
+      <c r="B1" s="3"/>
+      <c r="C1" s="3"/>
+      <c r="D1" s="3"/>
+      <c r="E1" s="3"/>
+      <c r="F1" s="3"/>
+      <c r="G1" s="3"/>
+      <c r="H1" s="3"/>
+      <c r="I1" s="3"/>
+      <c r="J1" s="3"/>
+      <c r="K1" s="3"/>
+      <c r="L1" s="3"/>
+      <c r="M1" s="3"/>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="2"/>
-      <c r="B2" s="2"/>
-      <c r="C2" s="2"/>
-      <c r="D2" s="2"/>
-      <c r="E2" s="2"/>
-      <c r="F2" s="2"/>
-      <c r="G2" s="2"/>
-      <c r="H2" s="2"/>
-      <c r="I2" s="2"/>
-      <c r="J2" s="2"/>
-      <c r="K2" s="2"/>
-      <c r="L2" s="2"/>
-      <c r="M2" s="2"/>
+      <c r="A2" s="3"/>
+      <c r="B2" s="3"/>
+      <c r="C2" s="3"/>
+      <c r="D2" s="3"/>
+      <c r="E2" s="3"/>
+      <c r="F2" s="3"/>
+      <c r="G2" s="3"/>
+      <c r="H2" s="3"/>
+      <c r="I2" s="3"/>
+      <c r="J2" s="3"/>
+      <c r="K2" s="3"/>
+      <c r="L2" s="3"/>
+      <c r="M2" s="3"/>
     </row>
     <row r="3" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="3" t="s">
+      <c r="A3" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="4" t="s">
+      <c r="B3" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="C3" s="4"/>
-      <c r="D3" s="4"/>
-      <c r="E3" s="4"/>
-      <c r="F3" s="4"/>
-      <c r="G3" s="4"/>
-      <c r="H3" s="4"/>
-      <c r="I3" s="4"/>
-      <c r="J3" s="4"/>
-      <c r="K3" s="4"/>
-      <c r="L3" s="4"/>
-      <c r="M3" s="4"/>
+      <c r="C3" s="5"/>
+      <c r="D3" s="5"/>
+      <c r="E3" s="5"/>
+      <c r="F3" s="5"/>
+      <c r="G3" s="5"/>
+      <c r="H3" s="5"/>
+      <c r="I3" s="5"/>
+      <c r="J3" s="5"/>
+      <c r="K3" s="5"/>
+      <c r="L3" s="5"/>
+      <c r="M3" s="5"/>
     </row>
     <row r="4" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="3" t="s">
+      <c r="A4" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="4" t="s">
+      <c r="B4" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="C4" s="4"/>
-      <c r="D4" s="4"/>
-      <c r="E4" s="4"/>
-      <c r="F4" s="4"/>
-      <c r="G4" s="4"/>
-      <c r="H4" s="4"/>
-      <c r="I4" s="4"/>
-      <c r="J4" s="4"/>
-      <c r="K4" s="4"/>
-      <c r="L4" s="4"/>
-      <c r="M4" s="4"/>
+      <c r="C4" s="5"/>
+      <c r="D4" s="5"/>
+      <c r="E4" s="5"/>
+      <c r="F4" s="5"/>
+      <c r="G4" s="5"/>
+      <c r="H4" s="5"/>
+      <c r="I4" s="5"/>
+      <c r="J4" s="5"/>
+      <c r="K4" s="5"/>
+      <c r="L4" s="5"/>
+      <c r="M4" s="5"/>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="2"/>
-      <c r="B5" s="2"/>
-      <c r="C5" s="2"/>
-      <c r="D5" s="2"/>
-      <c r="E5" s="2"/>
-      <c r="F5" s="2"/>
-      <c r="G5" s="2"/>
-      <c r="H5" s="2"/>
-      <c r="I5" s="2"/>
-      <c r="J5" s="2"/>
-      <c r="K5" s="2"/>
-      <c r="L5" s="2"/>
-      <c r="M5" s="2"/>
+      <c r="A5" s="3"/>
+      <c r="B5" s="3"/>
+      <c r="C5" s="3"/>
+      <c r="D5" s="3"/>
+      <c r="E5" s="3"/>
+      <c r="F5" s="3"/>
+      <c r="G5" s="3"/>
+      <c r="H5" s="3"/>
+      <c r="I5" s="3"/>
+      <c r="J5" s="3"/>
+      <c r="K5" s="3"/>
+      <c r="L5" s="3"/>
+      <c r="M5" s="3"/>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="2"/>
-      <c r="B6" s="5" t="s">
+      <c r="A6" s="3"/>
+      <c r="B6" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="C6" s="2"/>
-      <c r="D6" s="2"/>
-      <c r="E6" s="2"/>
-      <c r="F6" s="2"/>
-      <c r="G6" s="2"/>
-      <c r="H6" s="2"/>
-      <c r="I6" s="2"/>
-      <c r="J6" s="2"/>
-      <c r="K6" s="2"/>
-      <c r="L6" s="2"/>
-      <c r="M6" s="2"/>
+      <c r="C6" s="3"/>
+      <c r="D6" s="3"/>
+      <c r="E6" s="3"/>
+      <c r="F6" s="3"/>
+      <c r="G6" s="3"/>
+      <c r="H6" s="3"/>
+      <c r="I6" s="3"/>
+      <c r="J6" s="3"/>
+      <c r="K6" s="3"/>
+      <c r="L6" s="3"/>
+      <c r="M6" s="3"/>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="2"/>
-      <c r="B7" s="6" t="s">
+      <c r="A7" s="3"/>
+      <c r="B7" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="C7" s="2"/>
-      <c r="D7" s="2"/>
-      <c r="E7" s="2"/>
-      <c r="F7" s="2"/>
-      <c r="G7" s="2"/>
-      <c r="H7" s="2"/>
-      <c r="I7" s="2"/>
-      <c r="J7" s="2"/>
-      <c r="K7" s="2"/>
-      <c r="L7" s="2"/>
-      <c r="M7" s="2"/>
+      <c r="C7" s="3"/>
+      <c r="D7" s="3"/>
+      <c r="E7" s="3"/>
+      <c r="F7" s="3"/>
+      <c r="G7" s="3"/>
+      <c r="H7" s="3"/>
+      <c r="I7" s="3"/>
+      <c r="J7" s="3"/>
+      <c r="K7" s="3"/>
+      <c r="L7" s="3"/>
+      <c r="M7" s="3"/>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="2"/>
-      <c r="B8" s="6" t="s">
+      <c r="A8" s="3"/>
+      <c r="B8" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="C8" s="2"/>
-      <c r="D8" s="2"/>
-      <c r="E8" s="2"/>
-      <c r="F8" s="2"/>
-      <c r="G8" s="2"/>
-      <c r="H8" s="2"/>
-      <c r="I8" s="2"/>
-      <c r="J8" s="2"/>
-      <c r="K8" s="2"/>
-      <c r="L8" s="2"/>
-      <c r="M8" s="2"/>
+      <c r="C8" s="3"/>
+      <c r="D8" s="3"/>
+      <c r="E8" s="3"/>
+      <c r="F8" s="3"/>
+      <c r="G8" s="3"/>
+      <c r="H8" s="3"/>
+      <c r="I8" s="3"/>
+      <c r="J8" s="3"/>
+      <c r="K8" s="3"/>
+      <c r="L8" s="3"/>
+      <c r="M8" s="3"/>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="2"/>
-      <c r="B9" s="6"/>
-      <c r="C9" s="2"/>
-      <c r="D9" s="2"/>
-      <c r="E9" s="2"/>
-      <c r="F9" s="2"/>
-      <c r="G9" s="2"/>
-      <c r="H9" s="2"/>
-      <c r="I9" s="2"/>
-      <c r="J9" s="2"/>
-      <c r="K9" s="2"/>
-      <c r="L9" s="2"/>
-      <c r="M9" s="2"/>
+      <c r="A9" s="3"/>
+      <c r="B9" s="7"/>
+      <c r="C9" s="3"/>
+      <c r="D9" s="3"/>
+      <c r="E9" s="3"/>
+      <c r="F9" s="3"/>
+      <c r="G9" s="3"/>
+      <c r="H9" s="3"/>
+      <c r="I9" s="3"/>
+      <c r="J9" s="3"/>
+      <c r="K9" s="3"/>
+      <c r="L9" s="3"/>
+      <c r="M9" s="3"/>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="2"/>
-      <c r="B10" s="5"/>
-      <c r="C10" s="2"/>
-      <c r="D10" s="2"/>
-      <c r="E10" s="2"/>
-      <c r="F10" s="2"/>
-      <c r="G10" s="2"/>
-      <c r="H10" s="2"/>
-      <c r="I10" s="2"/>
-      <c r="J10" s="2"/>
-      <c r="K10" s="2"/>
-      <c r="L10" s="2"/>
-      <c r="M10" s="2"/>
-    </row>
-    <row r="11" s="8" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="7"/>
-      <c r="B11" s="5" t="s">
+      <c r="A10" s="3"/>
+      <c r="B10" s="6"/>
+      <c r="C10" s="3"/>
+      <c r="D10" s="3"/>
+      <c r="E10" s="3"/>
+      <c r="F10" s="3"/>
+      <c r="G10" s="3"/>
+      <c r="H10" s="3"/>
+      <c r="I10" s="3"/>
+      <c r="J10" s="3"/>
+      <c r="K10" s="3"/>
+      <c r="L10" s="3"/>
+      <c r="M10" s="3"/>
+    </row>
+    <row r="11" s="9" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="8"/>
+      <c r="B11" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="C11" s="7"/>
-      <c r="D11" s="7"/>
-      <c r="E11" s="7"/>
-      <c r="F11" s="7"/>
-      <c r="G11" s="7"/>
-      <c r="H11" s="7"/>
-      <c r="I11" s="7"/>
-      <c r="J11" s="7"/>
-      <c r="K11" s="7"/>
-      <c r="L11" s="7"/>
-      <c r="M11" s="7"/>
+      <c r="C11" s="8"/>
+      <c r="D11" s="8"/>
+      <c r="E11" s="8"/>
+      <c r="F11" s="8"/>
+      <c r="G11" s="8"/>
+      <c r="H11" s="8"/>
+      <c r="I11" s="8"/>
+      <c r="J11" s="8"/>
+      <c r="K11" s="8"/>
+      <c r="L11" s="8"/>
+      <c r="M11" s="8"/>
     </row>
     <row r="12" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="2"/>
-      <c r="B12" s="2"/>
-      <c r="C12" s="2"/>
-      <c r="D12" s="2"/>
-      <c r="E12" s="2"/>
-      <c r="F12" s="2"/>
-      <c r="G12" s="2"/>
-      <c r="H12" s="2"/>
-      <c r="I12" s="2"/>
-      <c r="J12" s="2"/>
-      <c r="K12" s="2"/>
-      <c r="L12" s="2"/>
-      <c r="M12" s="2"/>
+      <c r="A12" s="3"/>
+      <c r="B12" s="3"/>
+      <c r="C12" s="3"/>
+      <c r="D12" s="3"/>
+      <c r="E12" s="3"/>
+      <c r="F12" s="3"/>
+      <c r="G12" s="3"/>
+      <c r="H12" s="3"/>
+      <c r="I12" s="3"/>
+      <c r="J12" s="3"/>
+      <c r="K12" s="3"/>
+      <c r="L12" s="3"/>
+      <c r="M12" s="3"/>
     </row>
     <row r="13" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="2"/>
-      <c r="B13" s="2"/>
-      <c r="C13" s="2"/>
-      <c r="D13" s="2"/>
-      <c r="E13" s="2"/>
-      <c r="F13" s="2"/>
-      <c r="G13" s="2"/>
-      <c r="H13" s="2"/>
-      <c r="I13" s="2"/>
-      <c r="J13" s="2"/>
-      <c r="K13" s="2"/>
-      <c r="L13" s="2"/>
-      <c r="M13" s="2"/>
+      <c r="A13" s="3"/>
+      <c r="B13" s="3"/>
+      <c r="C13" s="3"/>
+      <c r="D13" s="3"/>
+      <c r="E13" s="3"/>
+      <c r="F13" s="3"/>
+      <c r="G13" s="3"/>
+      <c r="H13" s="3"/>
+      <c r="I13" s="3"/>
+      <c r="J13" s="3"/>
+      <c r="K13" s="3"/>
+      <c r="L13" s="3"/>
+      <c r="M13" s="3"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -1404,25 +1363,20 @@
   <dimension ref="A1:N24"/>
   <sheetFormatPr defaultColWidth="8.859375" defaultRowHeight="12.75" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="9" width="16.14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="2" style="9" width="11.29"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="9" width="11"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="9" width="11.29"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="9" width="11.14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="9" width="9.71"/>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16384" min="15" style="9" width="8.86"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="10" width="16.14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="2" style="10" width="11.29"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="10" width="11"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="10" width="11.29"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="10" width="11.14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="10" width="9.71"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16384" min="15" style="10" width="8.86"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="33" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="10" t="s">
+      <c r="A1" s="11" t="s">
         <v>9</v>
       </c>
-      <c r="B1" s="10"/>
-      <c r="C1" s="11"/>
-      <c r="D1" s="11"/>
-      <c r="E1" s="11"/>
-      <c r="F1" s="11"/>
-      <c r="G1" s="11"/>
+      <c r="B1" s="11"/>
       <c r="K1" s="12"/>
     </row>
     <row r="2" customFormat="false" ht="53.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2197,7 +2151,7 @@
       <c r="L21" s="21"/>
       <c r="M21" s="24"/>
     </row>
-    <row r="22" s="8" customFormat="true" ht="72" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="22" s="9" customFormat="true" ht="72" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="25" t="s">
         <v>42</v>
       </c>
@@ -2214,38 +2168,38 @@
       <c r="L22" s="25"/>
       <c r="M22" s="25"/>
     </row>
-    <row r="23" s="8" customFormat="true" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A23" s="26" t="s">
+    <row r="23" s="9" customFormat="true" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A23" s="25" t="s">
         <v>43</v>
       </c>
-      <c r="B23" s="26"/>
-      <c r="C23" s="26"/>
-      <c r="D23" s="26"/>
-      <c r="E23" s="26"/>
-      <c r="F23" s="26"/>
-      <c r="G23" s="26"/>
-      <c r="H23" s="26"/>
-      <c r="I23" s="26"/>
-      <c r="J23" s="26"/>
-      <c r="K23" s="26"/>
-      <c r="L23" s="26"/>
-      <c r="M23" s="26"/>
-    </row>
-    <row r="24" s="29" customFormat="true" ht="28.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A24" s="27"/>
-      <c r="B24" s="28"/>
-      <c r="C24" s="28"/>
-      <c r="D24" s="28"/>
-      <c r="E24" s="28"/>
-      <c r="F24" s="28"/>
-      <c r="G24" s="28"/>
-      <c r="H24" s="28"/>
-      <c r="I24" s="28"/>
-      <c r="J24" s="28"/>
-      <c r="K24" s="28"/>
-      <c r="L24" s="28"/>
-      <c r="M24" s="28"/>
-      <c r="N24" s="28"/>
+      <c r="B23" s="25"/>
+      <c r="C23" s="25"/>
+      <c r="D23" s="25"/>
+      <c r="E23" s="25"/>
+      <c r="F23" s="25"/>
+      <c r="G23" s="25"/>
+      <c r="H23" s="25"/>
+      <c r="I23" s="25"/>
+      <c r="J23" s="25"/>
+      <c r="K23" s="25"/>
+      <c r="L23" s="25"/>
+      <c r="M23" s="25"/>
+    </row>
+    <row r="24" s="28" customFormat="true" ht="28.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A24" s="26"/>
+      <c r="B24" s="27"/>
+      <c r="C24" s="27"/>
+      <c r="D24" s="27"/>
+      <c r="E24" s="27"/>
+      <c r="F24" s="27"/>
+      <c r="G24" s="27"/>
+      <c r="H24" s="27"/>
+      <c r="I24" s="27"/>
+      <c r="J24" s="27"/>
+      <c r="K24" s="27"/>
+      <c r="L24" s="27"/>
+      <c r="M24" s="27"/>
+      <c r="N24" s="27"/>
     </row>
   </sheetData>
   <mergeCells count="4">
@@ -2276,39 +2230,39 @@
   <dimension ref="A1:P23"/>
   <sheetFormatPr defaultColWidth="8.859375" defaultRowHeight="13.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="9" width="16.14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="2" style="9" width="11.29"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="9" width="11.43"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="9" width="10.71"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="9" width="10"/>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="15" min="15" style="9" width="8.86"/>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16383" min="17" style="9" width="8.86"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16384" min="16384" style="9" width="11.53"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="10" width="16.14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="2" style="10" width="11.29"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="10" width="11.43"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="10" width="10.71"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="10" width="10"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="15" min="15" style="10" width="8.86"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16383" min="17" style="10" width="8.86"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16384" min="16384" style="10" width="11.53"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="33" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="10" t="s">
+      <c r="A1" s="11" t="s">
         <v>9</v>
       </c>
-      <c r="B1" s="10"/>
-      <c r="C1" s="30"/>
+      <c r="B1" s="11"/>
+      <c r="C1" s="29"/>
       <c r="L1" s="12"/>
     </row>
     <row r="2" customFormat="false" ht="53.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="31" t="s">
+      <c r="A2" s="30" t="s">
         <v>44</v>
       </c>
-      <c r="B2" s="31"/>
-      <c r="C2" s="31"/>
-      <c r="D2" s="31"/>
-      <c r="E2" s="31"/>
-      <c r="F2" s="31"/>
-      <c r="G2" s="31"/>
-      <c r="H2" s="31"/>
-      <c r="I2" s="31"/>
+      <c r="B2" s="30"/>
+      <c r="C2" s="30"/>
+      <c r="D2" s="30"/>
+      <c r="E2" s="30"/>
+      <c r="F2" s="30"/>
+      <c r="G2" s="30"/>
+      <c r="H2" s="30"/>
+      <c r="I2" s="30"/>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="32"/>
+      <c r="A3" s="31"/>
       <c r="B3" s="16" t="s">
         <v>45</v>
       </c>
@@ -2347,6 +2301,9 @@
       </c>
       <c r="N3" s="16" t="s">
         <v>22</v>
+      </c>
+      <c r="O3" s="16" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2392,6 +2349,9 @@
       <c r="N4" s="18" t="n">
         <v>68.4524639093103</v>
       </c>
+      <c r="O4" s="10" t="n">
+        <v>63.7</v>
+      </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="17" t="s">
@@ -2529,43 +2489,43 @@
       <c r="A8" s="17" t="s">
         <v>28</v>
       </c>
-      <c r="B8" s="33" t="n">
+      <c r="B8" s="32" t="n">
         <v>96.5542024035849</v>
       </c>
-      <c r="C8" s="33" t="n">
+      <c r="C8" s="32" t="n">
         <v>98.4756835266645</v>
       </c>
-      <c r="D8" s="33" t="n">
+      <c r="D8" s="32" t="n">
         <v>96.5045605117129</v>
       </c>
-      <c r="E8" s="33" t="n">
+      <c r="E8" s="32" t="n">
         <v>95.3969352924801</v>
       </c>
-      <c r="F8" s="33" t="n">
+      <c r="F8" s="32" t="n">
         <v>95.7420670245576</v>
       </c>
-      <c r="G8" s="33" t="n">
+      <c r="G8" s="32" t="n">
         <v>97.3957109959814</v>
       </c>
-      <c r="H8" s="33" t="n">
+      <c r="H8" s="32" t="n">
         <v>99.3352283050497</v>
       </c>
-      <c r="I8" s="33" t="n">
+      <c r="I8" s="32" t="n">
         <v>88.4561217762903</v>
       </c>
-      <c r="J8" s="33" t="n">
+      <c r="J8" s="32" t="n">
         <v>97.1610357127359</v>
       </c>
-      <c r="K8" s="33" t="n">
+      <c r="K8" s="32" t="n">
         <v>92.2923641663514</v>
       </c>
-      <c r="L8" s="33" t="n">
+      <c r="L8" s="32" t="n">
         <v>96.8310713438811</v>
       </c>
-      <c r="M8" s="34" t="n">
+      <c r="M8" s="33" t="n">
         <v>97.8043034288077</v>
       </c>
-      <c r="N8" s="33" t="n">
+      <c r="N8" s="32" t="n">
         <v>99.0584377992885</v>
       </c>
     </row>
@@ -2573,43 +2533,43 @@
       <c r="A9" s="17" t="s">
         <v>29</v>
       </c>
-      <c r="B9" s="33" t="n">
+      <c r="B9" s="32" t="n">
         <v>102.319582536245</v>
       </c>
-      <c r="C9" s="33" t="n">
+      <c r="C9" s="32" t="n">
         <v>100.290900075893</v>
       </c>
-      <c r="D9" s="33" t="n">
+      <c r="D9" s="32" t="n">
         <v>99.4799345076142</v>
       </c>
-      <c r="E9" s="33" t="n">
+      <c r="E9" s="32" t="n">
         <v>99.7586044986661</v>
       </c>
-      <c r="F9" s="33" t="n">
+      <c r="F9" s="32" t="n">
         <v>101.9414811432</v>
       </c>
-      <c r="G9" s="33" t="n">
+      <c r="G9" s="32" t="n">
         <v>102.008550673194</v>
       </c>
-      <c r="H9" s="33" t="n">
+      <c r="H9" s="32" t="n">
         <v>98.5652614692592</v>
       </c>
-      <c r="I9" s="33" t="n">
+      <c r="I9" s="32" t="n">
         <v>97.9953810461989</v>
       </c>
-      <c r="J9" s="33" t="n">
+      <c r="J9" s="32" t="n">
         <v>98.3424324451653</v>
       </c>
-      <c r="K9" s="33" t="n">
+      <c r="K9" s="32" t="n">
         <v>97.9328039625694</v>
       </c>
-      <c r="L9" s="33" t="n">
+      <c r="L9" s="32" t="n">
         <v>101.163080399191</v>
       </c>
-      <c r="M9" s="34" t="n">
+      <c r="M9" s="33" t="n">
         <v>102.067756980505</v>
       </c>
-      <c r="N9" s="33" t="n">
+      <c r="N9" s="32" t="n">
         <v>100.608628489841</v>
       </c>
     </row>
@@ -2617,88 +2577,88 @@
       <c r="A10" s="17" t="s">
         <v>30</v>
       </c>
-      <c r="B10" s="33" t="n">
+      <c r="B10" s="32" t="n">
         <v>101.336491521858</v>
       </c>
-      <c r="C10" s="33" t="n">
+      <c r="C10" s="32" t="n">
         <v>104.211735157775</v>
       </c>
-      <c r="D10" s="33" t="n">
+      <c r="D10" s="32" t="n">
         <v>105.493739859828</v>
       </c>
-      <c r="E10" s="33" t="n">
+      <c r="E10" s="32" t="n">
         <v>105.518346578185</v>
       </c>
-      <c r="F10" s="33" t="n">
+      <c r="F10" s="32" t="n">
         <v>104.996951454684</v>
       </c>
-      <c r="G10" s="33" t="n">
+      <c r="G10" s="32" t="n">
         <v>102.652562142526</v>
       </c>
-      <c r="H10" s="33" t="n">
+      <c r="H10" s="32" t="n">
         <v>104.912016756824</v>
       </c>
-      <c r="I10" s="33" t="n">
+      <c r="I10" s="32" t="n">
         <v>108.344735183853</v>
       </c>
-      <c r="J10" s="33" t="n">
+      <c r="J10" s="32" t="n">
         <v>105.56401738172</v>
       </c>
-      <c r="K10" s="33" t="n">
+      <c r="K10" s="32" t="n">
         <v>104.419173338434</v>
       </c>
-      <c r="L10" s="33" t="n">
+      <c r="L10" s="32" t="n">
         <v>104.294565457398</v>
       </c>
-      <c r="M10" s="34" t="n">
+      <c r="M10" s="33" t="n">
         <v>100.93764263223</v>
       </c>
-      <c r="N10" s="33" t="n">
+      <c r="N10" s="32" t="n">
         <v>102.109203955676</v>
       </c>
-      <c r="O10" s="35"/>
+      <c r="O10" s="34"/>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="20" t="s">
         <v>31</v>
       </c>
-      <c r="B11" s="36" t="n">
+      <c r="B11" s="35" t="n">
         <v>107.544490032808</v>
       </c>
-      <c r="C11" s="36" t="n">
+      <c r="C11" s="35" t="n">
         <v>107.633610405133</v>
       </c>
-      <c r="D11" s="36" t="n">
+      <c r="D11" s="35" t="n">
         <v>105.718535411141</v>
       </c>
-      <c r="E11" s="36" t="n">
+      <c r="E11" s="35" t="n">
         <v>105.582308497105</v>
       </c>
-      <c r="F11" s="36" t="n">
+      <c r="F11" s="35" t="n">
         <v>107.439615961119</v>
       </c>
-      <c r="G11" s="36" t="n">
+      <c r="G11" s="35" t="n">
         <v>107.62824264732</v>
       </c>
-      <c r="H11" s="36" t="n">
+      <c r="H11" s="35" t="n">
         <v>108.117510377008</v>
       </c>
-      <c r="I11" s="36" t="n">
+      <c r="I11" s="35" t="n">
         <v>96.2909924841164</v>
       </c>
-      <c r="J11" s="36" t="n">
+      <c r="J11" s="35" t="n">
         <v>108.737981546524</v>
       </c>
-      <c r="K11" s="36" t="n">
+      <c r="K11" s="35" t="n">
         <v>99.8547943267006</v>
       </c>
-      <c r="L11" s="36" t="n">
+      <c r="L11" s="35" t="n">
         <v>108.951965685678</v>
       </c>
-      <c r="M11" s="37" t="n">
+      <c r="M11" s="36" t="n">
         <v>107.661855835372</v>
       </c>
-      <c r="N11" s="36" t="n">
+      <c r="N11" s="35" t="n">
         <v>108.048305050448</v>
       </c>
     </row>
@@ -2706,43 +2666,43 @@
       <c r="A12" s="17" t="s">
         <v>32</v>
       </c>
-      <c r="B12" s="33" t="n">
+      <c r="B12" s="32" t="n">
         <v>103.687863330247</v>
       </c>
-      <c r="C12" s="33" t="n">
+      <c r="C12" s="32" t="n">
         <v>103.648233259625</v>
       </c>
-      <c r="D12" s="33" t="n">
+      <c r="D12" s="32" t="n">
         <v>103.76546625421</v>
       </c>
-      <c r="E12" s="33" t="n">
+      <c r="E12" s="32" t="n">
         <v>103.605502983469</v>
       </c>
-      <c r="F12" s="33" t="n">
+      <c r="F12" s="32" t="n">
         <v>102.050534825459</v>
       </c>
-      <c r="G12" s="33" t="n">
+      <c r="G12" s="32" t="n">
         <v>103.54797059365</v>
       </c>
-      <c r="H12" s="33" t="n">
+      <c r="H12" s="32" t="n">
         <v>105.327301394896</v>
       </c>
-      <c r="I12" s="33" t="n">
+      <c r="I12" s="32" t="n">
         <v>107.712995613649</v>
       </c>
-      <c r="J12" s="33" t="n">
+      <c r="J12" s="32" t="n">
         <v>102.757781308564</v>
       </c>
-      <c r="K12" s="33" t="n">
+      <c r="K12" s="32" t="n">
         <v>104.938023368468</v>
       </c>
-      <c r="L12" s="33" t="n">
+      <c r="L12" s="32" t="n">
         <v>104.581200986088</v>
       </c>
-      <c r="M12" s="34" t="n">
+      <c r="M12" s="33" t="n">
         <v>105.187919752745</v>
       </c>
-      <c r="N12" s="33" t="n">
+      <c r="N12" s="32" t="n">
         <v>104.496524513642</v>
       </c>
     </row>
@@ -2750,43 +2710,43 @@
       <c r="A13" s="17" t="s">
         <v>33</v>
       </c>
-      <c r="B13" s="33" t="n">
+      <c r="B13" s="32" t="n">
         <v>101.75382799277</v>
       </c>
-      <c r="C13" s="33" t="n">
+      <c r="C13" s="32" t="n">
         <v>101.708532727252</v>
       </c>
-      <c r="D13" s="33" t="n">
+      <c r="D13" s="32" t="n">
         <v>102.266628268771</v>
       </c>
-      <c r="E13" s="33" t="n">
+      <c r="E13" s="32" t="n">
         <v>104.517136059781</v>
       </c>
-      <c r="F13" s="33" t="n">
+      <c r="F13" s="32" t="n">
         <v>105.712895782176</v>
       </c>
-      <c r="G13" s="33" t="n">
+      <c r="G13" s="32" t="n">
         <v>103.565040246611</v>
       </c>
-      <c r="H13" s="33" t="n">
+      <c r="H13" s="32" t="n">
         <v>102.981186013268</v>
       </c>
-      <c r="I13" s="33" t="n">
+      <c r="I13" s="32" t="n">
         <v>104.552529353774</v>
       </c>
-      <c r="J13" s="33" t="n">
+      <c r="J13" s="32" t="n">
         <v>102.37700485177</v>
       </c>
-      <c r="K13" s="33" t="n">
+      <c r="K13" s="32" t="n">
         <v>103.974955404868</v>
       </c>
-      <c r="L13" s="33" t="n">
+      <c r="L13" s="32" t="n">
         <v>103.865075413844</v>
       </c>
-      <c r="M13" s="34" t="n">
+      <c r="M13" s="33" t="n">
         <v>101.320789851119</v>
       </c>
-      <c r="N13" s="33" t="n">
+      <c r="N13" s="32" t="n">
         <v>101.335871253031</v>
       </c>
     </row>
@@ -2794,43 +2754,43 @@
       <c r="A14" s="17" t="s">
         <v>34</v>
       </c>
-      <c r="B14" s="33" t="n">
+      <c r="B14" s="32" t="n">
         <v>103.188630743001</v>
       </c>
-      <c r="C14" s="33" t="n">
+      <c r="C14" s="32" t="n">
         <v>104.885977468042</v>
       </c>
-      <c r="D14" s="33" t="n">
+      <c r="D14" s="32" t="n">
         <v>105.149879965517</v>
       </c>
-      <c r="E14" s="33" t="n">
+      <c r="E14" s="32" t="n">
         <v>104.33430871688</v>
       </c>
-      <c r="F14" s="33" t="n">
+      <c r="F14" s="32" t="n">
         <v>104.41692563556</v>
       </c>
-      <c r="G14" s="33" t="n">
+      <c r="G14" s="32" t="n">
         <v>104.019608450776</v>
       </c>
-      <c r="H14" s="33" t="n">
+      <c r="H14" s="32" t="n">
         <v>105.679932415061</v>
       </c>
-      <c r="I14" s="33" t="n">
+      <c r="I14" s="32" t="n">
         <v>106.793570975655</v>
       </c>
-      <c r="J14" s="33" t="n">
+      <c r="J14" s="32" t="n">
         <v>107.353620142912</v>
       </c>
-      <c r="K14" s="33" t="n">
+      <c r="K14" s="32" t="n">
         <v>105.110752619406</v>
       </c>
-      <c r="L14" s="33" t="n">
+      <c r="L14" s="32" t="n">
         <v>106.029076184307</v>
       </c>
-      <c r="M14" s="34" t="n">
+      <c r="M14" s="33" t="n">
         <v>107.01189444848</v>
       </c>
-      <c r="N14" s="33" t="n">
+      <c r="N14" s="32" t="n">
         <v>107.559880872064</v>
       </c>
     </row>
@@ -2838,43 +2798,43 @@
       <c r="A15" s="20" t="s">
         <v>35</v>
       </c>
-      <c r="B15" s="36" t="n">
+      <c r="B15" s="35" t="n">
         <v>107.772851442553</v>
       </c>
-      <c r="C15" s="36" t="n">
+      <c r="C15" s="35" t="n">
         <v>109.60042530612</v>
       </c>
-      <c r="D15" s="36" t="n">
+      <c r="D15" s="35" t="n">
         <v>110.8194210602</v>
       </c>
-      <c r="E15" s="36" t="n">
+      <c r="E15" s="35" t="n">
         <v>112.113102951014</v>
       </c>
-      <c r="F15" s="36" t="n">
+      <c r="F15" s="35" t="n">
         <v>111.746662069694</v>
       </c>
-      <c r="G15" s="36" t="n">
+      <c r="G15" s="35" t="n">
         <v>110.045184349404</v>
       </c>
-      <c r="H15" s="36" t="n">
+      <c r="H15" s="35" t="n">
         <v>112.464541500655</v>
       </c>
-      <c r="I15" s="36" t="n">
+      <c r="I15" s="35" t="n">
         <v>118.888656339685</v>
       </c>
-      <c r="J15" s="36" t="n">
+      <c r="J15" s="35" t="n">
         <v>110.25212139032</v>
       </c>
-      <c r="K15" s="36" t="n">
+      <c r="K15" s="35" t="n">
         <v>111.982554269098</v>
       </c>
-      <c r="L15" s="36" t="n">
+      <c r="L15" s="35" t="n">
         <v>112.975438421885</v>
       </c>
-      <c r="M15" s="37" t="n">
+      <c r="M15" s="36" t="n">
         <v>110.022580718448</v>
       </c>
-      <c r="N15" s="36" t="n">
+      <c r="N15" s="35" t="n">
         <v>109.824872305489</v>
       </c>
     </row>
@@ -2882,43 +2842,43 @@
       <c r="A16" s="17" t="s">
         <v>36</v>
       </c>
-      <c r="B16" s="33" t="n">
+      <c r="B16" s="32" t="n">
         <v>102.44487560074</v>
       </c>
-      <c r="C16" s="33" t="n">
+      <c r="C16" s="32" t="n">
         <v>100.697393808538</v>
       </c>
-      <c r="D16" s="33" t="n">
+      <c r="D16" s="32" t="n">
         <v>101.057019111063</v>
       </c>
-      <c r="E16" s="33" t="n">
+      <c r="E16" s="32" t="n">
         <v>101.305486041529</v>
       </c>
-      <c r="F16" s="33" t="n">
+      <c r="F16" s="32" t="n">
         <v>98.6716974999452</v>
       </c>
-      <c r="G16" s="33" t="n">
+      <c r="G16" s="32" t="n">
         <v>102.042509862083</v>
       </c>
-      <c r="H16" s="33" t="n">
+      <c r="H16" s="32" t="n">
         <v>102.314909587467</v>
       </c>
-      <c r="I16" s="33" t="n">
+      <c r="I16" s="32" t="n">
         <v>99.4258777245868</v>
       </c>
-      <c r="J16" s="33" t="n">
+      <c r="J16" s="32" t="n">
         <v>101.041428402787</v>
       </c>
-      <c r="K16" s="33" t="n">
+      <c r="K16" s="32" t="n">
         <v>101.43368366786</v>
       </c>
-      <c r="L16" s="33" t="n">
+      <c r="L16" s="32" t="n">
         <v>100.398874096472</v>
       </c>
-      <c r="M16" s="34" t="n">
+      <c r="M16" s="33" t="n">
         <v>101.831540253394</v>
       </c>
-      <c r="N16" s="33" t="n">
+      <c r="N16" s="32" t="n">
         <v>102.797847974988</v>
       </c>
     </row>
@@ -2926,43 +2886,43 @@
       <c r="A17" s="17" t="s">
         <v>37</v>
       </c>
-      <c r="B17" s="33" t="n">
+      <c r="B17" s="32" t="n">
         <v>97.6458794302131</v>
       </c>
-      <c r="C17" s="33" t="n">
+      <c r="C17" s="32" t="n">
         <v>96.5420964494174</v>
       </c>
-      <c r="D17" s="33" t="n">
+      <c r="D17" s="32" t="n">
         <v>96.2640464261831</v>
       </c>
-      <c r="E17" s="33" t="n">
+      <c r="E17" s="32" t="n">
         <v>98.727523008994</v>
       </c>
-      <c r="F17" s="33" t="n">
+      <c r="F17" s="32" t="n">
         <v>97.5429851779669</v>
       </c>
-      <c r="G17" s="33" t="n">
+      <c r="G17" s="32" t="n">
         <v>95.3464548537252</v>
       </c>
-      <c r="H17" s="33" t="n">
+      <c r="H17" s="32" t="n">
         <v>92.6154929919146</v>
       </c>
-      <c r="I17" s="33" t="n">
+      <c r="I17" s="32" t="n">
         <v>96.2872888273213</v>
       </c>
-      <c r="J17" s="33" t="n">
+      <c r="J17" s="32" t="n">
         <v>97.2487578296707</v>
       </c>
-      <c r="K17" s="33" t="n">
+      <c r="K17" s="32" t="n">
         <v>97.9784939495012</v>
       </c>
-      <c r="L17" s="33" t="n">
+      <c r="L17" s="32" t="n">
         <v>95.296355603057</v>
       </c>
-      <c r="M17" s="34" t="n">
+      <c r="M17" s="33" t="n">
         <v>94.9793313297627</v>
       </c>
-      <c r="N17" s="33" t="n">
+      <c r="N17" s="32" t="n">
         <v>93.1</v>
       </c>
     </row>
@@ -2970,43 +2930,43 @@
       <c r="A18" s="17" t="s">
         <v>38</v>
       </c>
-      <c r="B18" s="33" t="n">
+      <c r="B18" s="32" t="n">
         <v>107.459240542102</v>
       </c>
-      <c r="C18" s="33" t="n">
+      <c r="C18" s="32" t="n">
         <v>110.350348961693</v>
       </c>
-      <c r="D18" s="33" t="n">
+      <c r="D18" s="32" t="n">
         <v>109.536133825715</v>
       </c>
-      <c r="E18" s="33" t="n">
+      <c r="E18" s="32" t="n">
         <v>106.791208547589</v>
       </c>
-      <c r="F18" s="33" t="n">
+      <c r="F18" s="32" t="n">
         <v>105.579615901293</v>
       </c>
-      <c r="G18" s="33" t="n">
+      <c r="G18" s="32" t="n">
         <v>108.715524661608</v>
       </c>
-      <c r="H18" s="33" t="n">
+      <c r="H18" s="32" t="n">
         <v>109.376516171662</v>
       </c>
-      <c r="I18" s="33" t="n">
+      <c r="I18" s="32" t="n">
         <v>114.038138350891</v>
       </c>
-      <c r="J18" s="33" t="n">
+      <c r="J18" s="32" t="n">
         <v>113.23916537132</v>
       </c>
-      <c r="K18" s="33" t="n">
+      <c r="K18" s="32" t="n">
         <v>111.632065537092</v>
       </c>
-      <c r="L18" s="33" t="n">
+      <c r="L18" s="32" t="n">
         <v>111.876607389617</v>
       </c>
-      <c r="M18" s="34" t="n">
+      <c r="M18" s="33" t="n">
         <v>116.825422916724</v>
       </c>
-      <c r="N18" s="33" t="n">
+      <c r="N18" s="32" t="n">
         <v>121.2</v>
       </c>
     </row>
@@ -3014,110 +2974,108 @@
       <c r="A19" s="20" t="s">
         <v>40</v>
       </c>
-      <c r="B19" s="36" t="n">
+      <c r="B19" s="35" t="n">
         <v>106.100825131711</v>
       </c>
-      <c r="C19" s="36" t="n">
+      <c r="C19" s="35" t="n">
         <v>105.572333398754</v>
       </c>
-      <c r="D19" s="36" t="n">
+      <c r="D19" s="35" t="n">
         <v>105.83145039346</v>
       </c>
-      <c r="E19" s="36" t="n">
+      <c r="E19" s="35" t="n">
         <v>107.157549037081</v>
       </c>
-      <c r="F19" s="36" t="n">
+      <c r="F19" s="35" t="n">
         <v>103.55222375223</v>
       </c>
-      <c r="G19" s="36" t="n">
+      <c r="G19" s="35" t="n">
         <v>105.588231916872</v>
       </c>
-      <c r="H19" s="36" t="n">
+      <c r="H19" s="35" t="n">
         <v>104.9588138138</v>
       </c>
-      <c r="I19" s="36" t="n">
+      <c r="I19" s="35" t="n">
         <v>107.462677360943</v>
       </c>
-      <c r="J19" s="36" t="n">
+      <c r="J19" s="35" t="n">
         <v>109.303978703826</v>
       </c>
-      <c r="K19" s="36" t="n">
+      <c r="K19" s="35" t="n">
         <v>108.764357494204</v>
       </c>
-      <c r="L19" s="36" t="n">
+      <c r="L19" s="35" t="n">
         <v>106.312151749179</v>
       </c>
-      <c r="M19" s="37" t="n">
+      <c r="M19" s="36" t="n">
         <v>109.054207201897</v>
       </c>
-      <c r="N19" s="36" t="n">
+      <c r="N19" s="35" t="n">
         <v>110.4</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="38"/>
-      <c r="B20" s="38"/>
-      <c r="C20" s="39"/>
-      <c r="D20" s="39"/>
-      <c r="E20" s="39"/>
-      <c r="F20" s="40"/>
-      <c r="G20" s="40"/>
+      <c r="A20" s="37"/>
+      <c r="B20" s="37"/>
+      <c r="C20" s="38"/>
+      <c r="D20" s="38"/>
+      <c r="E20" s="38"/>
       <c r="L20" s="21"/>
     </row>
-    <row r="21" s="8" customFormat="true" ht="72" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A21" s="41" t="s">
+    <row r="21" s="9" customFormat="true" ht="72" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A21" s="39" t="s">
         <v>46</v>
       </c>
-      <c r="B21" s="41"/>
-      <c r="C21" s="41"/>
-      <c r="D21" s="41"/>
-      <c r="E21" s="41"/>
-      <c r="F21" s="41"/>
-      <c r="G21" s="41"/>
-      <c r="H21" s="41"/>
-      <c r="I21" s="41"/>
-      <c r="J21" s="41"/>
-      <c r="K21" s="41"/>
-      <c r="L21" s="41"/>
-      <c r="M21" s="41"/>
-      <c r="N21" s="41"/>
-      <c r="P21" s="0"/>
-    </row>
-    <row r="22" s="8" customFormat="true" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A22" s="42" t="s">
+      <c r="B21" s="39"/>
+      <c r="C21" s="39"/>
+      <c r="D21" s="39"/>
+      <c r="E21" s="39"/>
+      <c r="F21" s="39"/>
+      <c r="G21" s="39"/>
+      <c r="H21" s="39"/>
+      <c r="I21" s="39"/>
+      <c r="J21" s="39"/>
+      <c r="K21" s="39"/>
+      <c r="L21" s="39"/>
+      <c r="M21" s="39"/>
+      <c r="N21" s="39"/>
+      <c r="P21" s="1"/>
+    </row>
+    <row r="22" s="9" customFormat="true" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A22" s="39" t="s">
         <v>47</v>
       </c>
-      <c r="B22" s="42"/>
-      <c r="C22" s="42"/>
-      <c r="D22" s="42"/>
-      <c r="E22" s="42"/>
-      <c r="F22" s="42"/>
-      <c r="G22" s="42"/>
-      <c r="H22" s="42"/>
-      <c r="I22" s="42"/>
-      <c r="J22" s="42"/>
-      <c r="K22" s="42"/>
-      <c r="L22" s="42"/>
-      <c r="M22" s="42"/>
-      <c r="N22" s="42"/>
-      <c r="P22" s="0"/>
-    </row>
-    <row r="23" s="29" customFormat="true" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A23" s="27"/>
-      <c r="B23" s="28"/>
-      <c r="C23" s="28"/>
-      <c r="D23" s="28"/>
-      <c r="E23" s="28"/>
-      <c r="F23" s="28"/>
-      <c r="G23" s="28"/>
-      <c r="H23" s="28"/>
-      <c r="I23" s="28"/>
-      <c r="J23" s="28"/>
-      <c r="K23" s="28"/>
-      <c r="L23" s="28"/>
-      <c r="M23" s="28"/>
-      <c r="N23" s="28"/>
-      <c r="P23" s="0"/>
+      <c r="B22" s="39"/>
+      <c r="C22" s="39"/>
+      <c r="D22" s="39"/>
+      <c r="E22" s="39"/>
+      <c r="F22" s="39"/>
+      <c r="G22" s="39"/>
+      <c r="H22" s="39"/>
+      <c r="I22" s="39"/>
+      <c r="J22" s="39"/>
+      <c r="K22" s="39"/>
+      <c r="L22" s="39"/>
+      <c r="M22" s="39"/>
+      <c r="N22" s="39"/>
+      <c r="P22" s="1"/>
+    </row>
+    <row r="23" s="28" customFormat="true" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A23" s="26"/>
+      <c r="B23" s="27"/>
+      <c r="C23" s="27"/>
+      <c r="D23" s="27"/>
+      <c r="E23" s="27"/>
+      <c r="F23" s="27"/>
+      <c r="G23" s="27"/>
+      <c r="H23" s="27"/>
+      <c r="I23" s="27"/>
+      <c r="J23" s="27"/>
+      <c r="K23" s="27"/>
+      <c r="L23" s="27"/>
+      <c r="M23" s="27"/>
+      <c r="N23" s="27"/>
+      <c r="P23" s="1"/>
     </row>
   </sheetData>
   <mergeCells count="4">
